--- a/Assets/Resources/NpcDialogDataBase.xlsx
+++ b/Assets/Resources/NpcDialogDataBase.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\SangDol\Assets\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\SangDol\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B1FA2E-F586-4BAC-BBFD-4EB83C67F671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11475"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NpcDialogDataBase" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="125">
   <si>
     <t>Dialog_ID</t>
   </si>
@@ -60,250 +61,408 @@
     <t>필요 시 Action 늘릴예정</t>
   </si>
   <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>Acion 종류</t>
+  </si>
+  <si>
+    <t>Action마다 다름</t>
+  </si>
+  <si>
+    <t>D_30001_002</t>
+  </si>
+  <si>
+    <t>D_30001_003</t>
+  </si>
+  <si>
+    <t>D_30001_005</t>
+  </si>
+  <si>
+    <t>D_30001_004</t>
+  </si>
+  <si>
+    <t>대화문의 ID</t>
+  </si>
+  <si>
+    <t>대화문을 사용하는 NPC의 ID</t>
+  </si>
+  <si>
+    <t>UI에 표시될 NPC의 이름</t>
+  </si>
+  <si>
+    <t>UI에 표시될 대화문 내용</t>
+  </si>
+  <si>
+    <t>다음 대화문 ID</t>
+  </si>
+  <si>
+    <t>선택지1에 나올 내용</t>
+  </si>
+  <si>
+    <t>선택지1 선택 시 다음에 나올 대화문 ID</t>
+  </si>
+  <si>
+    <t>선택지2에 나올 내용</t>
+  </si>
+  <si>
+    <t>선택지2 선택 시 다음에 나올 대화문 ID</t>
+  </si>
+  <si>
+    <t>해당 대화문에서 해야할 Action</t>
+  </si>
+  <si>
+    <t>Action의 매개변수</t>
+  </si>
+  <si>
+    <t>Action의 의미</t>
+  </si>
+  <si>
+    <t>D_NpcID_000</t>
+  </si>
+  <si>
+    <t>30001~39999</t>
+  </si>
+  <si>
+    <t>선택지 존재 시 공백</t>
+  </si>
+  <si>
+    <t>Quest_Show</t>
+  </si>
+  <si>
+    <t>퀘스트ID(string)</t>
+  </si>
+  <si>
+    <t>퀘스트 미리보기</t>
+  </si>
+  <si>
+    <t>D_30001_006</t>
+  </si>
+  <si>
+    <t>대화 종료 시 END</t>
+  </si>
+  <si>
+    <t>Quest_Accept</t>
+  </si>
+  <si>
+    <t>퀘스트 수락</t>
+  </si>
+  <si>
+    <t>D_30001_007</t>
+  </si>
+  <si>
+    <t>Q_30001_001</t>
+  </si>
+  <si>
+    <t>Quest_Refuse</t>
+  </si>
+  <si>
+    <t>없음</t>
+  </si>
+  <si>
+    <t>퀘스트 거절</t>
+  </si>
+  <si>
+    <t>Quest_Clear</t>
+  </si>
+  <si>
+    <t>퀘스트 클리어</t>
+  </si>
+  <si>
+    <t>???</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>드디어 정신을 차렸군. 자네가 숲 속에 쓰러져 있길래 아이가 데리고 왔다더군.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>누구…십니까…?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>이런, 내 소개가 늦었군. 난 하버라고 하네. 이 마을의 촌장이지.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>자네는 누구인가? 우리 마을 사람은 아닌듯 한데…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>너는 {PlaterName}이라고 합니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그렇군. 우리 마을은 평화로운 마을이니 편하게 쉬다 가게나.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>제가 도와드릴 일이 있을까요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>구해주셔서 감사합니다. 먼저 일어나 보겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>몸 조심 하시게.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>END</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30001_006</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>허허..은혜를 갚을 줄 아는 사람이구만? 안그래도 마리아가 고민이 있다고 하던데 조금 도와줄 수 있겠나?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>네, 제가 가서 도와드리겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30001_007</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quest_Show</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quest_Accept</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼 부탁하네 마리아는 바로 옆집에 살고있으니, 한번 찾아가보게.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>마리아</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>하버</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이고 허리야…이놈의 촌장을 빨리 때려 쳐야지 원…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30002_001</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>오늘 저녁은 어떤걸 만들어볼까?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30002_002</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>촌장님께 얘기 들었어요. 저희 일을 도와주신다고요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30002_003</t>
+  </si>
+  <si>
+    <t>저희도 공짜로 도움을 받지는 않을거에요. 도와주신다면 소소한 보상을 드릴게요!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30002_004</t>
+  </si>
+  <si>
+    <t>D_30002_004</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>먼저 저 대신 상인한테 가서 잘 익은 사과 하나만 구해주세요. 이번에 사과가 풍년이라서 공짜로 나눠준다고 하더라구요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q_30001_002</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>알겠습니다. 상인은 어디있죠?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>제가 급한일이 생겨서…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30002_005</t>
+  </si>
+  <si>
+    <t>D_30002_006</t>
+  </si>
+  <si>
+    <t>D_30002_009</t>
+  </si>
+  <si>
+    <t>마을 입구쪽으로 가면 볼 수 있어요! 그럼 부탁드릴게요~</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아…네…알겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>D_30001_001</t>
-  </si>
-  <si>
-    <t>촌장</t>
-  </si>
-  <si>
-    <t>우리 마을에 온 것을 환영하네 모험가여.</t>
-  </si>
-  <si>
-    <t>String</t>
-  </si>
-  <si>
-    <t>Acion 종류</t>
-  </si>
-  <si>
-    <t>Action마다 다름</t>
-  </si>
-  <si>
-    <t>D_30001_002</t>
-  </si>
-  <si>
-    <t>요즘 몸 상태가 예전같지 않구만…</t>
-  </si>
-  <si>
-    <t>END</t>
-  </si>
-  <si>
-    <t>D_30001_003</t>
-  </si>
-  <si>
-    <t>반갑소</t>
-  </si>
-  <si>
-    <t>반갑습니다. 누구십니까?</t>
-  </si>
-  <si>
-    <t>D_30001_005</t>
-  </si>
-  <si>
-    <t>말걸지 마십쇼.</t>
-  </si>
-  <si>
-    <t>D_30001_004</t>
-  </si>
-  <si>
-    <t>대화문의 ID</t>
-  </si>
-  <si>
-    <t>대화문을 사용하는 NPC의 ID</t>
-  </si>
-  <si>
-    <t>UI에 표시될 NPC의 이름</t>
-  </si>
-  <si>
-    <t>UI에 표시될 대화문 내용</t>
-  </si>
-  <si>
-    <t>다음 대화문 ID</t>
-  </si>
-  <si>
-    <t>선택지1에 나올 내용</t>
-  </si>
-  <si>
-    <t>선택지1 선택 시 다음에 나올 대화문 ID</t>
-  </si>
-  <si>
-    <t>선택지2에 나올 내용</t>
-  </si>
-  <si>
-    <t>선택지2 선택 시 다음에 나올 대화문 ID</t>
-  </si>
-  <si>
-    <t>해당 대화문에서 해야할 Action</t>
-  </si>
-  <si>
-    <t>Action의 매개변수</t>
-  </si>
-  <si>
-    <t>Action의 의미</t>
-  </si>
-  <si>
-    <t>허허 싸가지가 없는 청년이구만. 꺼지게.</t>
-  </si>
-  <si>
-    <t>D_NpcID_000</t>
-  </si>
-  <si>
-    <t>30001~39999</t>
-  </si>
-  <si>
-    <t>선택지 존재 시 공백</t>
-  </si>
-  <si>
-    <t>Quest_Show</t>
-  </si>
-  <si>
-    <t>퀘스트ID(string)</t>
-  </si>
-  <si>
-    <t>퀘스트 미리보기</t>
-  </si>
-  <si>
-    <t>이 마을의 촌장이라네. 처음보는 청년인데 우리 마을은 처음오는건가?</t>
-  </si>
-  <si>
-    <t>네, 오늘 아침에 들어왔습니다.</t>
-  </si>
-  <si>
-    <t>D_30001_006</t>
-  </si>
-  <si>
-    <t>대화 종료 시 END</t>
-  </si>
-  <si>
-    <t>Quest_Accept</t>
-  </si>
-  <si>
-    <t>퀘스트 수락</t>
-  </si>
-  <si>
-    <t>그러면 마을 적응도 할겸 내 부탁 하나만 들어주겠는가? 보수는 당연히 주지.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>상인</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>없는거 빼고 다 있습니다~</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30003_001</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>벌써 다녀오신건가요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Quest_Clear</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>감사합니다! 보상으로 사과로 방금 만든 체력 포션을 드릴게요!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30002_010</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아 그리고, 다일씨가 고민이 있는거 같은데 한번 가보시면 좋을거같아요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30004_001</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>다일</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30001_008</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30002_008</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>요즘 화살값이 너무 올랐어…아 방금 한 말은 무시해주면 고맙겠네.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30004_002</t>
+  </si>
+  <si>
+    <t>D_30004_003</t>
+  </si>
+  <si>
+    <t>D_30004_004</t>
+  </si>
+  <si>
+    <t>D_30004_005</t>
+  </si>
+  <si>
+    <t>D_30004_006</t>
+  </si>
+  <si>
+    <t>D_30004_007</t>
+  </si>
+  <si>
+    <t>D_30004_008</t>
+  </si>
+  <si>
+    <t>D_30004_009</t>
+  </si>
+  <si>
+    <t>D_30004_010</t>
+  </si>
+  <si>
+    <t>오! 당신이군요. 촌장님께 얘기 들었습니다! 마을 사람들을 도와주고 계신다면서요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">제발 저의 부탁도 들어주세요…. </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅁ…무슨일이신데요…?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30004_004</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아 갑자기 급한일이…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>들어주기 싫으면 그냥 싫다고 말씀을 하세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>정말 감사합니다…드디어…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>요즘들어 밤마다 마을 앞에 있는 카르보나 숲에서 저놈의 늑ㄱ…아니 늑대들이 시끄럽게 울어대고 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>최근에 늑대가 많이 늘어서 그런거 같은데, 한 5마리만 잡아서 개체수를 관리해야 할 것 같습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q_30001_003</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜 나만…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>싫습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>네, 도와드리겠습니다.</t>
-  </si>
-  <si>
-    <t>D_30001_008</t>
-  </si>
-  <si>
-    <t>아 제가 할 일이 있습니다.</t>
-  </si>
-  <si>
-    <t>D_30001_007</t>
-  </si>
-  <si>
-    <t>Q_30001_001</t>
-  </si>
-  <si>
-    <t>Quest_Refuse</t>
-  </si>
-  <si>
-    <t>없음</t>
-  </si>
-  <si>
-    <t>퀘스트 거절</t>
-  </si>
-  <si>
-    <t>아쉽구만. 나중에라도 마음이 바뀌면 부탁함세.</t>
-  </si>
-  <si>
-    <t>Quest_Clear</t>
-  </si>
-  <si>
-    <t>퀘스트 클리어</t>
-  </si>
-  <si>
-    <t>자세한 부탁은 이 쪽지에 적어 놨으니, 확인해보게. 잘 부탁하네 청년.</t>
-  </si>
-  <si>
-    <t>D_30001_009</t>
-  </si>
-  <si>
-    <t>아직도 안갔나?</t>
-  </si>
-  <si>
-    <t>D_30001_010</t>
-  </si>
-  <si>
-    <t>오 갔다왔는가?</t>
-  </si>
-  <si>
-    <t>네. 부탁하신 일 전부 끝냈습니다.</t>
-  </si>
-  <si>
-    <t>D_30001_011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">고맙네 </t>
-  </si>
-  <si>
-    <t>D_30001_012</t>
-  </si>
-  <si>
-    <t>슬라임좀 잡아줘</t>
-  </si>
-  <si>
-    <t>넹</t>
-  </si>
-  <si>
-    <t>D_30001_014</t>
-  </si>
-  <si>
-    <t>싫어요</t>
-  </si>
-  <si>
-    <t>D_30001_013</t>
-  </si>
-  <si>
-    <t>Q_30001_002</t>
-  </si>
-  <si>
-    <t>그럼 꺼지쇼</t>
-  </si>
-  <si>
-    <t>수고좀 해줘</t>
-  </si>
-  <si>
-    <t>D_30001_015</t>
-  </si>
-  <si>
-    <t>D_30001_016</t>
-  </si>
-  <si>
-    <t>D_30001_017</t>
-  </si>
-  <si>
-    <t>D_30001_018</t>
-  </si>
-  <si>
-    <t>밥좀 줘</t>
-  </si>
-  <si>
-    <t>D_30001_020</t>
-  </si>
-  <si>
-    <t>D_30001_019</t>
-  </si>
-  <si>
-    <t>Q_30001_003</t>
-  </si>
-  <si>
-    <t>D_30001_021</t>
-  </si>
-  <si>
-    <t>D_30001_022</t>
-  </si>
-  <si>
-    <t>D_30001_023</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼 부탁드리겠습니다. 카르보나 숲은 마을 밖으로 나가는 길을 따라가면 있을겁니다!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>감사합니다. 드디어 밤에 좀 편히 잘 수 있을거같네요. 보수는 여기있습니다! 도움이 될겁니다!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1376,10 +1535,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="112.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="45.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="27.625" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="23.5" bestFit="1" customWidth="1"/>
@@ -1436,66 +1605,72 @@
     </row>
     <row r="2" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="B2">
         <v>30001</v>
       </c>
       <c r="C2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" t="s">
+        <v>13</v>
+      </c>
+      <c r="U2" t="s">
+        <v>13</v>
+      </c>
+      <c r="V2" t="s">
+        <v>13</v>
+      </c>
+      <c r="W2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="X2" t="s">
         <v>15</v>
-      </c>
-      <c r="N2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>16</v>
-      </c>
-      <c r="R2" t="s">
-        <v>16</v>
-      </c>
-      <c r="S2" t="s">
-        <v>16</v>
-      </c>
-      <c r="T2" t="s">
-        <v>16</v>
-      </c>
-      <c r="U2" t="s">
-        <v>16</v>
-      </c>
-      <c r="V2" t="s">
-        <v>16</v>
-      </c>
-      <c r="W2" t="s">
-        <v>17</v>
-      </c>
-      <c r="X2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>30001</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>0</v>
@@ -1533,177 +1708,171 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B4">
         <v>30001</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
+      <c r="R4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G4" t="s">
+      <c r="S4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H4" t="s">
+      <c r="T4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I4" t="s">
+      <c r="U4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="V4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="X4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="Y4" t="s">
         <v>31</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="V4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="X4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>30001</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
+        <v>55</v>
+      </c>
+      <c r="F5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="X5" s="6" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="Y5" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>30001</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" t="s">
-        <v>49</v>
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>59</v>
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="X6" s="6" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="Y6" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B7">
         <v>30001</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J7" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="K7" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="1"/>
@@ -1715,33 +1884,36 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
       <c r="W7" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="X7" s="6" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="Y7" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B8">
         <v>30001</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="J8" t="s">
-        <v>59</v>
+        <v>40</v>
+      </c>
+      <c r="K8" t="s">
+        <v>43</v>
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="8"/>
@@ -1753,125 +1925,113 @@
       <c r="U8" s="8"/>
       <c r="V8" s="8"/>
       <c r="W8" s="8" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="Y8" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="B9">
         <v>30001</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" t="s">
-        <v>51</v>
-      </c>
-      <c r="K9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B10">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B11">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" t="s">
-        <v>71</v>
+        <v>73</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B12">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" t="s">
-        <v>63</v>
-      </c>
-      <c r="K12" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B13">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="J13" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="K13" t="s">
         <v>79</v>
@@ -1879,42 +2039,39 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B14">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B15">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="J15" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="K15" t="s">
         <v>79</v>
@@ -1922,39 +2079,42 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B16">
-        <v>30001</v>
+        <v>30003</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>88</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="B17">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" t="s">
         <v>84</v>
+      </c>
+      <c r="J17" t="s">
+        <v>92</v>
+      </c>
+      <c r="K17" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -1962,157 +2122,239 @@
         <v>84</v>
       </c>
       <c r="B18">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D18" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" t="s">
-        <v>63</v>
-      </c>
-      <c r="K18" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B19">
-        <v>30001</v>
+        <v>30002</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D19" t="s">
-        <v>86</v>
-      </c>
-      <c r="F19" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" t="s">
-        <v>87</v>
-      </c>
-      <c r="H19" t="s">
-        <v>77</v>
-      </c>
-      <c r="I19" t="s">
-        <v>88</v>
-      </c>
-      <c r="J19" t="s">
-        <v>44</v>
-      </c>
-      <c r="K19" t="s">
-        <v>89</v>
+        <v>95</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B20">
-        <v>30001</v>
+        <v>30004</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="B21">
-        <v>30001</v>
+        <v>30004</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" t="s">
-        <v>51</v>
-      </c>
-      <c r="K21" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="B22">
-        <v>30001</v>
+        <v>30004</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="D22" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" t="s">
-        <v>21</v>
+        <v>111</v>
+      </c>
+      <c r="F22" t="s">
+        <v>112</v>
+      </c>
+      <c r="G22" t="s">
+        <v>113</v>
+      </c>
+      <c r="H22" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B23">
-        <v>30001</v>
+        <v>30004</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" t="s">
-        <v>92</v>
+        <v>115</v>
+      </c>
+      <c r="E23" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24">
+        <v>30004</v>
+      </c>
+      <c r="C24" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25">
+        <v>30004</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>106</v>
+      </c>
+      <c r="B26">
+        <v>30004</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>118</v>
+      </c>
+      <c r="F26" t="s">
+        <v>122</v>
+      </c>
+      <c r="G26" t="s">
+        <v>108</v>
+      </c>
+      <c r="H26" t="s">
+        <v>121</v>
+      </c>
+      <c r="I26" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26" t="s">
+        <v>64</v>
+      </c>
+      <c r="K26" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27">
+        <v>30004</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28">
+        <v>30004</v>
+      </c>
+      <c r="C28" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" t="s">
+        <v>59</v>
+      </c>
+      <c r="J28" t="s">
+        <v>40</v>
+      </c>
+      <c r="K28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29">
+        <v>30004</v>
+      </c>
+      <c r="C29" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" t="s">
+        <v>59</v>
+      </c>
+      <c r="J29" t="s">
         <v>92</v>
       </c>
-      <c r="B24">
-        <v>30001</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" t="s">
-        <v>72</v>
-      </c>
-      <c r="E24" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" t="s">
-        <v>63</v>
-      </c>
-      <c r="K24" t="s">
-        <v>89</v>
+      <c r="K29" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/NpcDialogDataBase.xlsx
+++ b/Assets/Resources/NpcDialogDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\SangDol\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B1FA2E-F586-4BAC-BBFD-4EB83C67F671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A145317-D8E1-452B-A8B2-8004BFB80128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NpcDialogDataBase" sheetId="1" r:id="rId1"/>
@@ -189,10 +189,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>너는 {PlaterName}이라고 합니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>그렇군. 우리 마을은 평화로운 마을이니 편하게 쉬다 가게나.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -456,6 +452,10 @@
   </si>
   <si>
     <t>감사합니다. 드디어 밤에 좀 편히 잘 수 있을거같네요. 보수는 여기있습니다! 도움이 될겁니다!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 {PlayerName}이라고 합니다.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="2" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B2">
         <v>30001</v>
@@ -1664,7 +1664,7 @@
         <v>30001</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
         <v>52</v>
@@ -1714,13 +1714,13 @@
         <v>30001</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
         <v>53</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="G4" t="s">
         <v>19</v>
@@ -1770,19 +1770,19 @@
         <v>30001</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" t="s">
         <v>55</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" t="s">
         <v>56</v>
-      </c>
-      <c r="G5" t="s">
-        <v>60</v>
-      </c>
-      <c r="H5" t="s">
-        <v>57</v>
       </c>
       <c r="I5" t="s">
         <v>18</v>
@@ -1820,13 +1820,13 @@
         <v>30001</v>
       </c>
       <c r="C6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" t="s">
         <v>58</v>
-      </c>
-      <c r="E6" t="s">
-        <v>59</v>
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="1"/>
@@ -1840,7 +1840,7 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="X6" s="6" t="s">
         <v>36</v>
@@ -1857,19 +1857,19 @@
         <v>30001</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" t="s">
         <v>61</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>62</v>
       </c>
-      <c r="G7" t="s">
+      <c r="J7" t="s">
         <v>63</v>
-      </c>
-      <c r="J7" t="s">
-        <v>64</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -1901,13 +1901,13 @@
         <v>30001</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J8" t="s">
         <v>40</v>
@@ -1936,53 +1936,53 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B9">
         <v>30001</v>
       </c>
       <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
         <v>68</v>
       </c>
-      <c r="D9" t="s">
-        <v>69</v>
-      </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10">
         <v>30002</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B11">
         <v>30002</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" t="s">
         <v>73</v>
       </c>
-      <c r="E11" t="s">
-        <v>74</v>
-      </c>
       <c r="J11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K11" t="s">
         <v>43</v>
@@ -1990,371 +1990,371 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B12">
         <v>30002</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B13">
         <v>30002</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" t="s">
+        <v>63</v>
+      </c>
+      <c r="K13" t="s">
         <v>78</v>
-      </c>
-      <c r="F13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" t="s">
-        <v>81</v>
-      </c>
-      <c r="I13" t="s">
-        <v>82</v>
-      </c>
-      <c r="J13" t="s">
-        <v>64</v>
-      </c>
-      <c r="K13" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14">
         <v>30002</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B15">
         <v>30002</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J15" t="s">
         <v>40</v>
       </c>
       <c r="K15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B16">
         <v>30003</v>
       </c>
       <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" t="s">
         <v>88</v>
       </c>
-      <c r="D16" t="s">
-        <v>89</v>
-      </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B17">
         <v>30002</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E17" t="s">
+        <v>83</v>
+      </c>
+      <c r="J17" t="s">
         <v>91</v>
       </c>
-      <c r="E17" t="s">
-        <v>84</v>
-      </c>
-      <c r="J17" t="s">
-        <v>92</v>
-      </c>
       <c r="K17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B18">
         <v>30002</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" t="s">
         <v>93</v>
-      </c>
-      <c r="E18" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B19">
         <v>30002</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B20">
         <v>30004</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B21">
         <v>30004</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B22">
         <v>30004</v>
       </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" t="s">
         <v>111</v>
       </c>
-      <c r="F22" t="s">
+      <c r="G22" t="s">
         <v>112</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>113</v>
       </c>
-      <c r="H22" t="s">
-        <v>114</v>
-      </c>
       <c r="I22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B23">
         <v>30004</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24">
         <v>30004</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B25">
         <v>30004</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B26">
         <v>30004</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" t="s">
+        <v>107</v>
+      </c>
+      <c r="H26" t="s">
+        <v>120</v>
+      </c>
+      <c r="I26" t="s">
+        <v>106</v>
+      </c>
+      <c r="J26" t="s">
+        <v>63</v>
+      </c>
+      <c r="K26" t="s">
         <v>118</v>
-      </c>
-      <c r="F26" t="s">
-        <v>122</v>
-      </c>
-      <c r="G26" t="s">
-        <v>108</v>
-      </c>
-      <c r="H26" t="s">
-        <v>121</v>
-      </c>
-      <c r="I26" t="s">
-        <v>107</v>
-      </c>
-      <c r="J26" t="s">
-        <v>64</v>
-      </c>
-      <c r="K26" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B27">
         <v>30004</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B28">
         <v>30004</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J28" t="s">
         <v>40</v>
       </c>
       <c r="K28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29">
         <v>30004</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/NpcDialogDataBase.xlsx
+++ b/Assets/Resources/NpcDialogDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\SangDol\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A145317-D8E1-452B-A8B2-8004BFB80128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E309FF-7000-45DE-AE26-BA6779035E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6660" yWindow="1770" windowWidth="19845" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NpcDialogDataBase" sheetId="1" r:id="rId1"/>
@@ -368,94 +368,96 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
+    <t>D_30004_003</t>
+  </si>
+  <si>
+    <t>D_30004_004</t>
+  </si>
+  <si>
+    <t>D_30004_005</t>
+  </si>
+  <si>
+    <t>D_30004_006</t>
+  </si>
+  <si>
+    <t>D_30004_007</t>
+  </si>
+  <si>
+    <t>D_30004_008</t>
+  </si>
+  <si>
+    <t>D_30004_009</t>
+  </si>
+  <si>
+    <t>오! 당신이군요. 촌장님께 얘기 들었습니다! 마을 사람들을 도와주고 계신다면서요?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">제발 저의 부탁도 들어주세요…. </t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㅁ…무슨일이신데요…?</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>D_30004_004</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>아 갑자기 급한일이…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>들어주기 싫으면 그냥 싫다고 말씀을 하세요.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>정말 감사합니다…드디어…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>요즘들어 밤마다 마을 앞에 있는 카르보나 숲에서 저놈의 늑ㄱ…아니 늑대들이 시끄럽게 울어대고 있습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Q_30001_003</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>왜 나만…</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>싫습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>네, 도와드리겠습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼 부탁드리겠습니다. 카르보나 숲은 마을 밖으로 나가는 길을 따라가면 있을겁니다!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>감사합니다. 드디어 밤에 좀 편히 잘 수 있을거같네요. 보수는 여기있습니다! 도움이 될겁니다!</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>저는 {PlayerName}이라고 합니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>D_30004_002</t>
-  </si>
-  <si>
-    <t>D_30004_003</t>
-  </si>
-  <si>
-    <t>D_30004_004</t>
-  </si>
-  <si>
-    <t>D_30004_005</t>
-  </si>
-  <si>
-    <t>D_30004_006</t>
-  </si>
-  <si>
-    <t>D_30004_007</t>
-  </si>
-  <si>
-    <t>D_30004_008</t>
-  </si>
-  <si>
-    <t>D_30004_009</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>최근에 늑대가 많이 늘어서 그런거 같은데, 한 5마리만 잡아서 개체 수를 관리해야 할 것 같습니다.</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>D_30004_010</t>
-  </si>
-  <si>
-    <t>오! 당신이군요. 촌장님께 얘기 들었습니다! 마을 사람들을 도와주고 계신다면서요?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">제발 저의 부탁도 들어주세요…. </t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>ㅁ…무슨일이신데요…?</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>D_30004_004</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>아 갑자기 급한일이…</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>들어주기 싫으면 그냥 싫다고 말씀을 하세요.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>정말 감사합니다…드디어…</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>요즘들어 밤마다 마을 앞에 있는 카르보나 숲에서 저놈의 늑ㄱ…아니 늑대들이 시끄럽게 울어대고 있습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>최근에 늑대가 많이 늘어서 그런거 같은데, 한 5마리만 잡아서 개체수를 관리해야 할 것 같습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>Q_30001_003</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>왜 나만…</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>싫습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>네, 도와드리겠습니다.</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>그럼 부탁드리겠습니다. 카르보나 숲은 마을 밖으로 나가는 길을 따라가면 있을겁니다!</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>감사합니다. 드디어 밤에 좀 편히 잘 수 있을거같네요. 보수는 여기있습니다! 도움이 될겁니다!</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>저는 {PlayerName}이라고 합니다.</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1720,7 +1722,7 @@
         <v>53</v>
       </c>
       <c r="F4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G4" t="s">
         <v>19</v>
@@ -2170,7 +2172,7 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="B21">
         <v>30004</v>
@@ -2179,15 +2181,15 @@
         <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B22">
         <v>30004</v>
@@ -2196,24 +2198,24 @@
         <v>96</v>
       </c>
       <c r="D22" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" t="s">
         <v>110</v>
       </c>
-      <c r="F22" t="s">
+      <c r="H22" t="s">
         <v>111</v>
       </c>
-      <c r="G22" t="s">
-        <v>112</v>
-      </c>
-      <c r="H22" t="s">
-        <v>113</v>
-      </c>
       <c r="I22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B23">
         <v>30004</v>
@@ -2222,7 +2224,7 @@
         <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
         <v>58</v>
@@ -2230,7 +2232,7 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24">
         <v>30004</v>
@@ -2239,15 +2241,15 @@
         <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25">
         <v>30004</v>
@@ -2256,15 +2258,15 @@
         <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26">
         <v>30004</v>
@@ -2273,30 +2275,30 @@
         <v>96</v>
       </c>
       <c r="D26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" t="s">
+        <v>106</v>
+      </c>
+      <c r="H26" t="s">
         <v>117</v>
       </c>
-      <c r="F26" t="s">
-        <v>121</v>
-      </c>
-      <c r="G26" t="s">
-        <v>107</v>
-      </c>
-      <c r="H26" t="s">
-        <v>120</v>
-      </c>
       <c r="I26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J26" t="s">
         <v>63</v>
       </c>
       <c r="K26" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27">
         <v>30004</v>
@@ -2305,7 +2307,7 @@
         <v>96</v>
       </c>
       <c r="D27" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s">
         <v>58</v>
@@ -2313,7 +2315,7 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B28">
         <v>30004</v>
@@ -2322,7 +2324,7 @@
         <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
         <v>58</v>
@@ -2331,12 +2333,12 @@
         <v>40</v>
       </c>
       <c r="K28" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B29">
         <v>30004</v>
@@ -2345,7 +2347,7 @@
         <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
         <v>58</v>
@@ -2354,7 +2356,7 @@
         <v>91</v>
       </c>
       <c r="K29" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
